--- a/민트샘 프로젝트.xlsx
+++ b/민트샘 프로젝트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danymac/Projects/kangmint/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4ADCCC2-A2C7-834D-BFA8-8170FBAE1A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7FF30A-389D-234A-ADAB-3C4C575D8BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3440" yWindow="2700" windowWidth="27700" windowHeight="16580" activeTab="1" xr2:uid="{A78E749E-AAA6-F94F-86ED-A10B9E1C6B55}"/>
+    <workbookView xWindow="2920" yWindow="-20320" windowWidth="26520" windowHeight="18100" activeTab="1" xr2:uid="{A78E749E-AAA6-F94F-86ED-A10B9E1C6B55}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="64">
   <si>
     <t>놀이활동</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -176,10 +176,6 @@
   </si>
   <si>
     <t>1. 알림장 : 글자수만 더 늘리면 될 것 같아요!</t>
-  </si>
-  <si>
-    <t>내역</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>완료 여부</t>
@@ -207,6 +203,113 @@
 입력을 하면 연령에 맞는 기준으로 생활기록부를 작성해주는 챗봇
 결과물 : 수면, 배변, 식사, 신체운동, 사회관계, 의사소통, 자연탐구, 
 예술경험 순으로 상, 중, 하 단계로 나뉘어서 나오도록.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;영유아 발달 평가 총평 챗봇&gt; 
+필수 입력란 : 만 ㅡ세, 신체활동/의사소통/사회관계/예술경험/자연탐구/
+생활습관(특별히 성장한 모습이나 변화된 모습, 평소 행동 등)
+입력을 하면 2024 개정 표준보육과정(0~2세)을 근거로 80줄 분량의
+전문적인 총평을 작성해주는 챗봇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;월간 평가 챗봇&gt;
+필수 입력란 : 이번 달 보육 주제와 아이들 연령(만 나이 기준),
+중심적으로 이루어진 놀이(예 : 물감 물놀이, 물총 놀이, 바다생물 탐색),
+아이들 자발적으로 확장된 놀이, 교사 지원 내용, 부모면담 내용, 다음 달
+확장 놀이 내용
+입력을 하면 놀이 중심 흐름과 2024 개정 표준보육과정 및 누리과정의
+취지를 반영하여 1,000자 가량의 자연스러운 월간 놀이 평가서 형태로 
+작성해주는 챗봇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;안전교육일지 지원 챗봇(보육일지 용)&gt;
+필수 입력란 : 연령, 안전교육 주제, 소주제 및 활동내용
+입력을 하면 8대 안전교육 주제를 기반으로 보육일지에 포함할 수 있는
+안전교육일지('안전교육 실행 및 평가'문단)를 350자 가량으로 작성해주는 
+챗봇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;견학 계획안 챗봇&gt;
+필수 입력란 : 장소, 연령 및 아동 수, 견학 내용
+입력을 하면 공식 홈페이지 및 신뢰할 수 있는 출처를 확인하고
+교차검증하여 실제 운영 중인 전시, 체험 내용을 반영하고 연령에 적합한
+활동만 선별함. 버스 이동, 귀원 후 점심 유모차 관련 내용을 제외함.
+2024 개정 표준보육과정 및 2019 개정 누리과정을 반영한 견학 목표와
+활동 평가를 작성해주는 챗봇
+결과물 : 장소, 연령 및 인원, 견학 목표 2개(각 3줄씩), 사전 준비5개,
+사전 활동 4개, 견학 활동(견학 전 준비 사항 확인 3개, 장소로 이동 2개,
+현장체험 5개, 복귀 3개), 사후 활동 5개, 활동 평가 300자 가량
+* 꼭 캡쳐본을 확인해주세요!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;행사계획안 챗봇&gt;
+필수 입력란 ; 행사명/연령 및 인원 / 교사 수/ 행사 내용/ 예산 /
+부모 참여 여부
+입력을 하면 2024 개정 표준보육 과정 및 2019 개정 누리과정의 취지를
+반영하여 행사 목표, 활동 평가, 안전과리 등을 전문적으로 구성해주는 챗봇
+결과물  행사명 / 행사일시 / 연령 및 인원/ 교사 수 / 장소/ 행사목표 /
+참여 인원 / 준비물 / 소요비용 / 사전 준비(세부 계획) / 사전 활동 /
+진행순서(조 편성) / 행사 내용(상세 시나리오) / 행사 활동 (교사 역할,
+시간, 활동명, 세부내용, 준비물) / 안전 관리 / 부모 안내 및 연계 /
+역할 분담 / 활동 평가 / 행사 전체 평가 / 추후 개선 및 확장 아이디어
+* 꼭 캡쳐본을 확인해주세요!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업내역</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인 시 여전히 요금제 나오는 랜딩페이지로 이동하는 것 수정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업 메뉴들 더 이쁘게 디자인화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>우측 상단에 이이서 작업하기 버튼 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>하단에 SNS (카톡, 인스타, 페북, X) 연계버튼 생성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>paddle 등록 위한 기본 이용약관, 개인정보처리방침, 환불 정책, 계정 삭제 안내 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>랜딩페이지 애니메이션 효과 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>랜딩페이지 '이렇게 나와요' 부분 수정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인 시 프로필 옆 요금제 별안보이는 부분 수정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인 시 랜딩페이지 문구 '버거운 작업들, 민트쌤과 함께 금방 작업해보아요' 로 수정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인 시, 캘린더 생성하여, 나의 월간 작업 내역 확인, 공휴일도 표기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">원생 관리? </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -219,7 +322,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -243,8 +346,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -257,8 +368,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -266,6 +383,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -275,7 +407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -298,10 +430,34 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -939,57 +1095,289 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35536800-AF4A-F74D-9D21-7746C219FAC7}">
-  <dimension ref="B1:C7"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="44.140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="8"/>
+    <col min="1" max="1" width="5.7109375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="69.85546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="7"/>
+    <col min="4" max="16384" width="10.7109375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="19">
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="1:3" s="7" customFormat="1">
+      <c r="A1" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:3" s="15" customFormat="1">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="15" customFormat="1">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="2:3" ht="19">
-      <c r="B2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="C3" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="15" customFormat="1">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="15" customFormat="1">
+      <c r="A5" s="13">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="15" customFormat="1">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" ht="114">
-      <c r="B3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" ht="57">
-      <c r="B4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="57">
-      <c r="B5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="209">
-      <c r="B7" s="7" t="s">
+      <c r="C6" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="15" customFormat="1">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>46</v>
       </c>
+      <c r="C7" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="15" customFormat="1">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="15" customFormat="1">
+      <c r="A9" s="13">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="15" customFormat="1">
+      <c r="A10" s="13">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="15" customFormat="1">
+      <c r="A11" s="13">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="19">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="9"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="9"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="9"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="9"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="9">
+        <v>26</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
